--- a/output/pdf_financials_xlsx/MBX.xlsx
+++ b/output/pdf_financials_xlsx/MBX.xlsx
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.691067</v>
+        <v>4.035877</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.277327</v>
+        <v>5.490589</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.820434</v>
+        <v>0.475624</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4.562246</v>
+        <v>0.348984</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.04614</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001996</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.484536</v>
+        <v>-2.438396</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.538449</v>
+        <v>-2.536453</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.484536</v>
+        <v>-2.438396</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.538449</v>
+        <v>-2.536453</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-69.70045090727098</v>
+        <v>-68.40605275612265</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-67.97010701122326</v>
+        <v>-67.91666164612261</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
         <v>0.547356</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.10418</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005415</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.05446</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.044358</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.095571</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.09266099999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>9.986312</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>13.488075</v>
@@ -2756,25 +2756,25 @@
         <v>0.547356</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.10418</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005415</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.05446</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.044358</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.095571</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.09266099999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>9.986312</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>13.488075</v>
@@ -3452,25 +3452,25 @@
         <v>0.419733</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.470819</v>
+        <v>0.366639</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.243354</v>
+        <v>0.237939</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.357243</v>
+        <v>0.302783</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.30657</v>
+        <v>0.262212</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.262646</v>
+        <v>0.167075</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.323159</v>
+        <v>0.230498</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>10.511857</v>
+        <v>0.525545</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.57758</v>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -63055,7 +63055,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -64663,7 +64663,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E562" s="5" t="n">
@@ -64867,7 +64867,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E564" s="5" t="n">

--- a/output/pdf_financials_xlsx/MBX.xlsx
+++ b/output/pdf_financials_xlsx/MBX.xlsx
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.204245</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -7744,19 +7744,19 @@
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>2.162428</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.90183</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>0.531674</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>3.137283</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -30327,7 +30327,11 @@
           <t>Additions to intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -39489,7 +39493,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -46188,7 +46196,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -53525,7 +53537,11 @@
           <t>Proceeds from Disposal of Property and Equipment</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E450" s="5" t="n">
         <v>0.204245</v>
       </c>
